--- a/public/plantillas/Contingencia_Liquidacion.xlsx
+++ b/public/plantillas/Contingencia_Liquidacion.xlsx
@@ -599,7 +599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:M26"/>
+  <dimension ref="B2:M27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -659,154 +659,111 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>3. Si hubo devoluciones o paradas no entregadas, elige el Motivo de Devolución de la lista.</t>
+          <t>3. Las columnas con ▼ tienen lista: haz clic en la celda y toca la flecha ▼ que aparece a la derecha.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>4. En Caja Abierta elige el Motivo Caja Abierta y, si lo sabes, el monto pendiente en Q.</t>
+          <t>4. Si hubo devoluciones o paradas no entregadas, elige el Motivo de Devolución de la lista.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>5. Escribe la fecha como DD/MM/AAAA y la hora como HH:MM (24 horas).</t>
+          <t>5. En Caja Abierta elige el Motivo Caja Abierta y, si lo sabes, el monto pendiente en Q.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>6. La ruta debe estar asignada (en la app o en el formato de Asignación). Self Service y Bolsón se liquidan sin camión.</t>
+          <t>6. Escribe la fecha como DD/MM/AAAA y la hora como HH:MM (24 horas).</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>7. No cambies los nombres de las columnas ni de la hoja. Guarda el archivo como .xlsx.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="3" t="inlineStr">
+          <t>7. La ruta debe estar asignada (en la app o en el formato de Asignación). Self Service y Bolsón se liquidan sin camión.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>8. No cambies los nombres de las columnas ni de la hoja. Guarda el archivo como .xlsx.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Ejemplo (NO se carga; llena la hoja de datos)</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="B15" s="5" t="inlineStr">
+    <row r="16" ht="32" customHeight="1">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Fecha Ruta</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>No. Ruta</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Agencia</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Modalidad</t>
         </is>
       </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>Cajas Entregadas</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>Cajas Devueltas</t>
         </is>
       </c>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr">
         <is>
           <t>Paradas Entregadas</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>Paradas No Entregadas</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Motivo Devolución</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Motivo Caja Abierta</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Auditor</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Hora Liquidación</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16" s="6" t="inlineStr">
-        <is>
-          <t>07/10/2026</t>
-        </is>
-      </c>
-      <c r="C16" s="6" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>Villa Nueva</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>Liquidada</t>
-        </is>
-      </c>
-      <c r="F16" s="6" t="n">
-        <v>340</v>
-      </c>
-      <c r="G16" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>26</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
-        <is>
-          <t>Negocio Cerrado</t>
-        </is>
-      </c>
-      <c r="K16" s="6" t="inlineStr"/>
-      <c r="L16" s="6" t="inlineStr">
-        <is>
-          <t>ANA MARTÍNEZ</t>
-        </is>
-      </c>
-      <c r="M16" s="6" t="inlineStr">
-        <is>
-          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -818,7 +775,7 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>1210</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
@@ -832,14 +789,22 @@
         </is>
       </c>
       <c r="F17" s="6" t="n">
-        <v>120</v>
+        <v>340</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-      <c r="J17" s="6" t="inlineStr"/>
+        <v>10</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Negocio Cerrado</t>
+        </is>
+      </c>
       <c r="K17" s="6" t="inlineStr"/>
       <c r="L17" s="6" t="inlineStr">
         <is>
@@ -848,7 +813,7 @@
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>17:40</t>
         </is>
       </c>
     </row>
@@ -860,7 +825,7 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1210</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
@@ -870,11 +835,11 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Caja Abierta</t>
+          <t>Liquidada</t>
         </is>
       </c>
       <c r="F18" s="6" t="n">
-        <v>300</v>
+        <v>120</v>
       </c>
       <c r="G18" s="6" t="n">
         <v>0</v>
@@ -882,59 +847,101 @@
       <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="n"/>
       <c r="J18" s="6" t="inlineStr"/>
-      <c r="K18" s="6" t="inlineStr">
+      <c r="K18" s="6" t="inlineStr"/>
+      <c r="L18" s="6" t="inlineStr">
+        <is>
+          <t>ANA MARTÍNEZ</t>
+        </is>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>07/10/2026</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Villa Nueva</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>Caja Abierta</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>300</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="6" t="n"/>
+      <c r="J19" s="6" t="inlineStr"/>
+      <c r="K19" s="6" t="inlineStr">
         <is>
           <t>Pendiente Validación de Boleta</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L19" s="6" t="inlineStr">
         <is>
           <t>LUIS RAMOS</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr">
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>18:10</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>Importante</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>• Este formato solo lo puede cargar un usuario ADMINISTRADOR en la app.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>• Carga este archivo junto con el de Asignación del mismo día para que la app aplique primero la salida y luego la liquidación.</t>
+          <t>• Este formato solo lo puede cargar un usuario ADMINISTRADOR en la app.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>• La app revisa cada fila antes de guardar y te muestra cuáles tienen error; nada se guarda hasta que confirmas.</t>
+          <t>• Carga este archivo junto con el de Asignación del mismo día para que la app aplique primero la salida y luego la liquidación.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
+          <t>• La app revisa cada fila antes de guardar y te muestra cuáles tienen error; nada se guarda hasta que confirmas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
           <t>• Una ruta ya liquidada en la app no se vuelve a liquidar (la fila se marca con error).</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Leyenda: encabezado ROJO con * = obligatorio · encabezado AZUL = opcional · pasa el mouse sobre cada encabezado para ver la ayuda.</t>
         </is>
@@ -986,12 +993,12 @@
       </c>
       <c r="C1" s="8" t="inlineStr">
         <is>
-          <t>Agencia *</t>
+          <t>Agencia * ▼</t>
         </is>
       </c>
       <c r="D1" s="8" t="inlineStr">
         <is>
-          <t>Modalidad *</t>
+          <t>Modalidad * ▼</t>
         </is>
       </c>
       <c r="E1" s="8" t="inlineStr">
@@ -1016,12 +1023,12 @@
       </c>
       <c r="I1" s="9" t="inlineStr">
         <is>
-          <t>Motivo Devolución</t>
+          <t>Motivo Devolución ▼</t>
         </is>
       </c>
       <c r="J1" s="9" t="inlineStr">
         <is>
-          <t>Motivo Caja Abierta</t>
+          <t>Motivo Caja Abierta ▼</t>
         </is>
       </c>
       <c r="K1" s="9" t="inlineStr">
@@ -9556,10 +9563,10 @@
     <dataValidation sqref="A2:A501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe la fecha como DD/MM/AAAA." type="date" operator="greaterThan">
       <formula1>DATE(2024,1,1)</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$A$2:$A$25</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
@@ -9574,10 +9581,10 @@
     <dataValidation sqref="H2:H501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$E$2:$E$13</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista." type="list">
+    <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$F$2:$F$12</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">

--- a/public/plantillas/Contingencia_Liquidacion.xlsx
+++ b/public/plantillas/Contingencia_Liquidacion.xlsx
@@ -9564,7 +9564,7 @@
       <formula1>DATE(2024,1,1)</formula1>
     </dataValidation>
     <dataValidation sqref="C2:C501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$A$2:$A$25</formula1>
+      <formula1>=Catalogos!$A$2:$A$26</formula1>
     </dataValidation>
     <dataValidation sqref="D2:D501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
       <formula1>=Catalogos!$D$2:$D$4</formula1>
@@ -9611,7 +9611,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -9997,6 +9997,13 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Atanasio</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/plantillas/Contingencia_Liquidacion.xlsx
+++ b/public/plantillas/Contingencia_Liquidacion.xlsx
@@ -9783,6 +9783,11 @@
           <t>Cocales</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ZV&amp;COLEGIOS</t>
+        </is>
+      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Ruta Bolsón</t>
@@ -9803,6 +9808,11 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>Cuyotenango</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>INSTITUCIONALES</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">

--- a/public/plantillas/Contingencia_Liquidacion.xlsx
+++ b/public/plantillas/Contingencia_Liquidacion.xlsx
@@ -9832,6 +9832,11 @@
           <t>El Progreso</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>Cliente Rechaza Pedido</t>

--- a/public/plantillas/Contingencia_Liquidacion.xlsx
+++ b/public/plantillas/Contingencia_Liquidacion.xlsx
@@ -9582,10 +9582,10 @@
       <formula1>0</formula1>
     </dataValidation>
     <dataValidation sqref="I2:I501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$E$2:$E$13</formula1>
+      <formula1>=Catalogos!$E$2:$E$16</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J501" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="Valor no válido" error="Elige un valor de la lista (flecha ▼)." promptTitle="Lista ▼" prompt="Toca la flecha ▼ de la celda para ver las opciones permitidas." type="list">
-      <formula1>=Catalogos!$F$2:$F$12</formula1>
+      <formula1>=Catalogos!$F$2:$F$15</formula1>
     </dataValidation>
     <dataValidation sqref="K2:K501" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" error="Escribe un número mayor o igual a 0." type="decimal" operator="greaterThanOrEqual">
       <formula1>0</formula1>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>No dio tiempo de entrega (Revisita)</t>
+          <t>Pendiente Envase / Cajilla</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -9873,7 +9873,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Pedido mal Digitado</t>
+          <t>Falta de Albarán / Contraseña</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>No Hizo Pedido</t>
+          <t>Refacturación</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Paso Bloqueado</t>
+          <t>No dio tiempo de entrega (Revisita)</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -9924,7 +9924,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ruta Bolsón (Rechazo)</t>
+          <t>Pedido mal Digitado</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pendiente Envase / Cajilla</t>
         </is>
       </c>
     </row>
@@ -9934,6 +9939,16 @@
           <t>Mercados Especiales</t>
         </is>
       </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>No Hizo Pedido</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Falta de Albarán / Contraseña</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -9941,11 +9956,26 @@
           <t>Naranjo</t>
         </is>
       </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Paso Bloqueado</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Refacturación</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
           <t>Playa Grande</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ruta Bolsón (Rechazo)</t>
         </is>
       </c>
     </row>
